--- a/details.xlsx
+++ b/details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\quotation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F3368B-2D25-4214-9F77-C81F1C9DCD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05AA9E00-D988-4219-8AD2-10245D225192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="665">
   <si>
     <t>POLICY INFO</t>
   </si>
@@ -36,9 +36,6 @@
     <t>ADD-ONS</t>
   </si>
   <si>
-    <t>PAYMENT</t>
-  </si>
-  <si>
     <t>Motor Category *</t>
   </si>
   <si>
@@ -126,6 +123,12 @@
     <t>Add-ons (comma separated)</t>
   </si>
   <si>
+    <t>Additional Discount (Yes/No)</t>
+  </si>
+  <si>
+    <t>Loading%</t>
+  </si>
+  <si>
     <t>Auto Pay (TRUE/FALSE)</t>
   </si>
   <si>
@@ -136,6 +139,69 @@
   </si>
   <si>
     <t>Policy Number</t>
+  </si>
+  <si>
+    <t>2W</t>
+  </si>
+  <si>
+    <t>Package</t>
+  </si>
+  <si>
+    <t>fin@zypp.app</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>NEW</t>
+  </si>
+  <si>
+    <t>CORPORATE</t>
+  </si>
+  <si>
+    <t>RAJASTHAN-JAIPUR</t>
+  </si>
+  <si>
+    <t>ODYSSE ELECTRIC VEHICLES PVT LTD - SNAP WITHOUT BATTERY (1.2 CC)</t>
+  </si>
+  <si>
+    <t>1 year</t>
+  </si>
+  <si>
+    <t>WDMS10C10C09CCOD01727</t>
+  </si>
+  <si>
+    <t>SLYDHF009SA005244</t>
+  </si>
+  <si>
+    <t>BycyShare Technologies Private Limited</t>
+  </si>
+  <si>
+    <t>Gram Mangyawas, Shri Nidhi vihar, Plot no 5, Tehsil Sanganer, Jaipur, Rajasthan 302029</t>
+  </si>
+  <si>
+    <t>08AAHCB3836D1ZU</t>
+  </si>
+  <si>
+    <t>JAIPUR</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>IDFC First Bank Ltd</t>
+  </si>
+  <si>
+    <t>Zero Depreciation Cover</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>4501118241</t>
   </si>
   <si>
     <t>Field Guide — What to fill in each column</t>
@@ -350,9 +416,6 @@
     <t>connected -&gt; motor -&gt; new -&gt; fetch_details -&gt; fill_details -&gt; get_quote -&gt; customize_opened -&gt; zero_dep -&gt; recalculated -&gt; submit_coverages -&gt; kyc -&gt; proceed -&gt; proposal_created -&gt; proposal_saved -&gt; payment_done</t>
   </si>
   <si>
-    <t>YES</t>
-  </si>
-  <si>
     <t>13/03/2026 11:21</t>
   </si>
   <si>
@@ -1928,65 +1991,49 @@
     <t>4441780098</t>
   </si>
   <si>
-    <t>2W</t>
-  </si>
-  <si>
-    <t>Package</t>
-  </si>
-  <si>
-    <t>fin@zypp.app</t>
-  </si>
-  <si>
-    <t>Rollover</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>CORPORATE</t>
-  </si>
-  <si>
-    <t>KARNATAKA-BANGALORE</t>
-  </si>
-  <si>
-    <t>E SPRINTO ETHICS AND VALUES - E SPRINTO HS WITHOUT BATTERY (1.2 CC)</t>
-  </si>
-  <si>
-    <t>1 year</t>
-  </si>
-  <si>
-    <t>HC2M6031849</t>
-  </si>
-  <si>
-    <t>MD9AHSBHC26873849</t>
-  </si>
-  <si>
-    <t>BycyShare Technologies Private Limited</t>
-  </si>
-  <si>
-    <t>GODWON1110022/F6, KAR -560048, Hoodi Main Road, Seetharampalya Road, Euro School
-Rd, NCPR Industrial Layout, Bengaluru, Bengaluru Urban, Karnataka, 560048</t>
-  </si>
-  <si>
-    <t>29AAHCB3836D1ZQ</t>
-  </si>
-  <si>
-    <t>KARNATAKA</t>
-  </si>
-  <si>
-    <t>IDFC First Bank Ltd</t>
-  </si>
-  <si>
-    <t>BANGALORE</t>
-  </si>
-  <si>
-    <t>Zero Depreciation</t>
-  </si>
-  <si>
-    <t>KA01</t>
+    <t>16/04/2026 12:59</t>
+  </si>
+  <si>
+    <t>connected</t>
+  </si>
+  <si>
+    <t>16/04/2026 13:00</t>
+  </si>
+  <si>
+    <t>Page.evaluate: Execution context was destroyed, most likely because of a navigation.</t>
+  </si>
+  <si>
+    <t>16/04/2026 13:07</t>
+  </si>
+  <si>
+    <t>17/04/2026 09:54</t>
+  </si>
+  <si>
+    <t>17/04/2026 14:25</t>
+  </si>
+  <si>
+    <t>Page.evaluate: SyntaxError: Invalid regular expression: missing /
+    at eval (&lt;anonymous&gt;)
+    at UtilityScript.evaluate (&lt;anonymous&gt;:290:30)
+    at UtilityScript.&lt;anonymous&gt; (&lt;anonymous&gt;:1:44)</t>
+  </si>
+  <si>
+    <t>17/04/2026 14:26</t>
+  </si>
+  <si>
+    <t>17/04/2026 14:28</t>
+  </si>
+  <si>
+    <t>Page.evaluate: SyntaxError: Invalid or unexpected token
+    at eval (&lt;anonymous&gt;)
+    at UtilityScript.evaluate (&lt;anonymous&gt;:290:30)
+    at UtilityScript.&lt;anonymous&gt; (&lt;anonymous&gt;:1:44)</t>
+  </si>
+  <si>
+    <t>20/04/2026 11:47</t>
+  </si>
+  <si>
+    <t>connected -&gt; motor -&gt; new -&gt; fetch_details -&gt; fill_details -&gt; get_quote -&gt; customize_opened -&gt; addons_selected -&gt; recalculated -&gt; submit_coverages -&gt; additional_discount -&gt; buy_now</t>
   </si>
 </sst>
 </file>
@@ -1996,7 +2043,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-809]d\ mmmm\ yyyy;@"/>
   </numFmts>
-  <fonts count="54" x14ac:knownFonts="1">
+  <fonts count="55" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2285,8 +2332,14 @@
       <sz val="10"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="120">
+  <fills count="123">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2885,8 +2938,23 @@
         <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="93">
+  <borders count="96">
     <border>
       <left/>
       <right/>
@@ -4274,11 +4342,56 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4665,37 +4778,40 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="120" borderId="93" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="121" borderId="94" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="122" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5024,7 +5140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ92"/>
+  <dimension ref="A1:AL92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -5036,7 +5152,7 @@
     <col min="7" max="7" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="67.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="61.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
@@ -5056,283 +5172,296 @@
     <col min="28" max="28" width="16.5703125" customWidth="1"/>
     <col min="29" max="29" width="18.28515625" customWidth="1"/>
     <col min="30" max="31" width="11" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="132"/>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
-      <c r="R1" s="132"/>
-      <c r="S1" s="132"/>
-      <c r="T1" s="132"/>
-      <c r="U1" s="132"/>
-      <c r="V1" s="132"/>
-      <c r="W1" s="132"/>
-      <c r="X1" s="132"/>
-      <c r="Y1" s="132"/>
-      <c r="Z1" s="132"/>
-      <c r="AA1" s="132"/>
-      <c r="AB1" s="132"/>
-      <c r="AC1" s="132"/>
-      <c r="AD1" s="132"/>
-      <c r="AE1" s="132"/>
-      <c r="AF1" s="132"/>
-      <c r="AG1" s="132"/>
-      <c r="AH1" s="132"/>
-    </row>
-    <row r="2" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E2" s="132" t="s">
+    <row r="1" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="138"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="138"/>
+      <c r="L1" s="138"/>
+      <c r="M1" s="138"/>
+      <c r="N1" s="138"/>
+      <c r="O1" s="138"/>
+      <c r="P1" s="138"/>
+      <c r="Q1" s="138"/>
+      <c r="R1" s="138"/>
+      <c r="S1" s="138"/>
+      <c r="T1" s="138"/>
+      <c r="U1" s="138"/>
+      <c r="V1" s="138"/>
+      <c r="W1" s="138"/>
+      <c r="X1" s="138"/>
+      <c r="Y1" s="138"/>
+      <c r="Z1" s="138"/>
+      <c r="AA1" s="138"/>
+      <c r="AB1" s="138"/>
+      <c r="AC1" s="138"/>
+      <c r="AD1" s="138"/>
+      <c r="AE1" s="138"/>
+      <c r="AF1" s="138"/>
+      <c r="AG1" s="138"/>
+      <c r="AH1" s="138"/>
+    </row>
+    <row r="2" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="132" t="s">
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
-      <c r="R2" s="132"/>
-      <c r="S2" s="133" t="s">
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="132"/>
-      <c r="U2" s="132"/>
-      <c r="V2" s="132"/>
-      <c r="W2" s="132"/>
-      <c r="X2" s="132"/>
-      <c r="Y2" s="132"/>
-      <c r="Z2" s="132"/>
-      <c r="AA2" s="132"/>
-      <c r="AB2" s="132"/>
-      <c r="AC2" s="132"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="138"/>
+      <c r="Y2" s="138"/>
+      <c r="Z2" s="138"/>
+      <c r="AA2" s="138"/>
+      <c r="AB2" s="138"/>
+      <c r="AC2" s="138"/>
       <c r="AD2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="AE2" s="134" t="s">
+      <c r="AE2" s="138"/>
+      <c r="AF2" s="138"/>
+      <c r="AG2" s="138"/>
+      <c r="AH2" s="138"/>
+    </row>
+    <row r="3" spans="1:38" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="AF2" s="132"/>
-      <c r="AG2" s="132"/>
-      <c r="AH2" s="132"/>
-    </row>
-    <row r="3" spans="1:36" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="120" t="s">
+      <c r="B3" s="120" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="120" t="s">
+      <c r="C3" s="120" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="120" t="s">
+      <c r="D3" s="120" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="120" t="s">
+      <c r="E3" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="120" t="s">
+      <c r="F3" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="120" t="s">
+      <c r="G3" s="120" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="120" t="s">
+      <c r="H3" s="120" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="120" t="s">
+      <c r="I3" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="121" t="s">
+      <c r="J3" s="122" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="122" t="s">
+      <c r="K3" s="122" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="L3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="24" t="s">
+      <c r="M3" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="123" t="s">
+      <c r="N3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="O3" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="P3" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="P3" s="25" t="s">
+      <c r="Q3" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="R3" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="R3" s="90" t="s">
+      <c r="S3" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="S3" s="26" t="s">
+      <c r="T3" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="T3" s="26" t="s">
+      <c r="U3" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="26" t="s">
+      <c r="V3" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="V3" s="26" t="s">
+      <c r="W3" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="X3" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="W3" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="X3" s="26" t="s">
+      <c r="Y3" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="Y3" s="88" t="s">
+      <c r="Z3" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="Z3" s="88" t="s">
+      <c r="AA3" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="AA3" s="88" t="s">
+      <c r="AB3" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="AB3" s="88" t="s">
+      <c r="AC3" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="AC3" s="88" t="s">
+      <c r="AD3" s="124" t="s">
         <v>32</v>
       </c>
-      <c r="AD3" s="124" t="s">
+      <c r="AE3" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="AE3" s="27" t="s">
+      <c r="AF3" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="AF3" s="23" t="s">
+      <c r="AG3" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="AG3" s="27" t="s">
+      <c r="AH3" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="AH3" s="44" t="s">
+      <c r="AI3" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="AI3" s="27"/>
-      <c r="AJ3" s="44"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>631</v>
+      <c r="AJ3" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK3" s="27"/>
+      <c r="AL3" s="44"/>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>632</v>
+        <v>40</v>
       </c>
       <c r="C4" s="125" t="s">
-        <v>633</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>634</v>
-      </c>
-      <c r="E4" s="125" t="s">
-        <v>635</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="E4" s="125"/>
       <c r="F4" s="125" t="s">
-        <v>636</v>
-      </c>
-      <c r="G4" s="137" t="s">
-        <v>650</v>
+        <v>43</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>44</v>
       </c>
       <c r="H4" s="125" t="s">
-        <v>637</v>
-      </c>
-      <c r="I4" s="125" t="s">
-        <v>638</v>
-      </c>
-      <c r="J4" t="s">
-        <v>639</v>
+        <v>45</v>
+      </c>
+      <c r="I4" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="58" t="s">
+        <v>47</v>
       </c>
       <c r="K4" s="125">
         <v>2026</v>
       </c>
       <c r="L4" t="s">
-        <v>640</v>
+        <v>48</v>
       </c>
       <c r="M4" s="125">
         <v>36908</v>
       </c>
-      <c r="P4" s="58" t="s">
-        <v>641</v>
-      </c>
-      <c r="Q4" s="58" t="s">
-        <v>642</v>
-      </c>
-      <c r="R4" s="131">
-        <v>560048</v>
-      </c>
-      <c r="S4" t="s">
-        <v>643</v>
+      <c r="P4" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q4" s="142" t="s">
+        <v>50</v>
+      </c>
+      <c r="R4" s="23">
+        <v>302039</v>
+      </c>
+      <c r="S4" s="137" t="s">
+        <v>51</v>
       </c>
       <c r="T4" s="56">
         <v>42955</v>
       </c>
-      <c r="U4" s="58" t="s">
-        <v>644</v>
+      <c r="U4" s="132" t="s">
+        <v>52</v>
       </c>
       <c r="V4" s="23">
         <v>9836231116</v>
       </c>
       <c r="W4" s="23" t="s">
-        <v>633</v>
-      </c>
-      <c r="X4">
-        <v>560048</v>
-      </c>
-      <c r="Y4" s="58" t="s">
-        <v>645</v>
-      </c>
-      <c r="Z4" s="125" t="s">
-        <v>646</v>
+        <v>41</v>
+      </c>
+      <c r="X4" s="23">
+        <v>302029</v>
+      </c>
+      <c r="Y4" s="132" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z4" s="133" t="s">
+        <v>54</v>
       </c>
       <c r="AA4" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB4" s="93" t="s">
-        <v>647</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>648</v>
-      </c>
-      <c r="AD4" s="125" t="s">
-        <v>649</v>
-      </c>
-      <c r="AE4" s="125" t="b">
+        <v>55</v>
+      </c>
+      <c r="AB4" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC4" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF4">
+        <v>0.7</v>
+      </c>
+      <c r="AG4" s="125" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" s="92"/>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AH4" s="92"/>
+      <c r="AI4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C5" s="125"/>
       <c r="E5" s="125"/>
       <c r="F5" s="125"/>
@@ -5351,10 +5480,10 @@
       <c r="Z5" s="125"/>
       <c r="AB5" s="93"/>
       <c r="AD5" s="125"/>
-      <c r="AE5" s="125"/>
-      <c r="AF5" s="92"/>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG5" s="125"/>
+      <c r="AH5" s="92"/>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C6" s="125"/>
       <c r="E6" s="125"/>
       <c r="F6" s="125"/>
@@ -5373,10 +5502,10 @@
       <c r="Z6" s="125"/>
       <c r="AB6" s="93"/>
       <c r="AD6" s="125"/>
-      <c r="AE6" s="125"/>
-      <c r="AF6" s="92"/>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG6" s="125"/>
+      <c r="AH6" s="92"/>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C7" s="125"/>
       <c r="E7" s="125"/>
       <c r="F7" s="125"/>
@@ -5395,10 +5524,10 @@
       <c r="Z7" s="125"/>
       <c r="AB7" s="93"/>
       <c r="AD7" s="125"/>
-      <c r="AE7" s="125"/>
-      <c r="AF7" s="92"/>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG7" s="125"/>
+      <c r="AH7" s="92"/>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C8" s="125"/>
       <c r="E8" s="125"/>
       <c r="F8" s="125"/>
@@ -5417,10 +5546,10 @@
       <c r="Z8" s="125"/>
       <c r="AB8" s="93"/>
       <c r="AD8" s="125"/>
-      <c r="AE8" s="125"/>
-      <c r="AF8" s="92"/>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG8" s="125"/>
+      <c r="AH8" s="92"/>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C9" s="125"/>
       <c r="E9" s="125"/>
       <c r="F9" s="125"/>
@@ -5439,10 +5568,10 @@
       <c r="Z9" s="125"/>
       <c r="AB9" s="93"/>
       <c r="AD9" s="125"/>
-      <c r="AE9" s="125"/>
-      <c r="AF9" s="92"/>
-    </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG9" s="125"/>
+      <c r="AH9" s="92"/>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C10" s="125"/>
       <c r="E10" s="125"/>
       <c r="F10" s="125"/>
@@ -5461,10 +5590,10 @@
       <c r="Z10" s="125"/>
       <c r="AB10" s="93"/>
       <c r="AD10" s="125"/>
-      <c r="AE10" s="125"/>
-      <c r="AF10" s="92"/>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG10" s="125"/>
+      <c r="AH10" s="92"/>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C11" s="125"/>
       <c r="E11" s="125"/>
       <c r="F11" s="125"/>
@@ -5483,10 +5612,10 @@
       <c r="Z11" s="125"/>
       <c r="AB11" s="93"/>
       <c r="AD11" s="125"/>
-      <c r="AE11" s="125"/>
-      <c r="AF11" s="92"/>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG11" s="125"/>
+      <c r="AH11" s="92"/>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C12" s="125"/>
       <c r="E12" s="125"/>
       <c r="F12" s="125"/>
@@ -5505,10 +5634,10 @@
       <c r="Z12" s="125"/>
       <c r="AB12" s="93"/>
       <c r="AD12" s="125"/>
-      <c r="AE12" s="125"/>
-      <c r="AF12" s="92"/>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG12" s="125"/>
+      <c r="AH12" s="92"/>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C13" s="125"/>
       <c r="E13" s="125"/>
       <c r="F13" s="125"/>
@@ -5527,10 +5656,10 @@
       <c r="Z13" s="125"/>
       <c r="AB13" s="93"/>
       <c r="AD13" s="125"/>
-      <c r="AE13" s="125"/>
-      <c r="AF13" s="92"/>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG13" s="125"/>
+      <c r="AH13" s="92"/>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C14" s="125"/>
       <c r="E14" s="125"/>
       <c r="F14" s="125"/>
@@ -5549,10 +5678,10 @@
       <c r="Z14" s="125"/>
       <c r="AB14" s="93"/>
       <c r="AD14" s="125"/>
-      <c r="AE14" s="125"/>
-      <c r="AF14" s="92"/>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG14" s="125"/>
+      <c r="AH14" s="92"/>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C15" s="125"/>
       <c r="E15" s="125"/>
       <c r="F15" s="125"/>
@@ -5571,10 +5700,10 @@
       <c r="Z15" s="125"/>
       <c r="AB15" s="93"/>
       <c r="AD15" s="125"/>
-      <c r="AE15" s="125"/>
-      <c r="AF15" s="92"/>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG15" s="125"/>
+      <c r="AH15" s="92"/>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C16" s="125"/>
       <c r="E16" s="125"/>
       <c r="F16" s="125"/>
@@ -5593,10 +5722,10 @@
       <c r="Z16" s="125"/>
       <c r="AB16" s="93"/>
       <c r="AD16" s="125"/>
-      <c r="AE16" s="125"/>
-      <c r="AF16" s="92"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG16" s="125"/>
+      <c r="AH16" s="92"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C17" s="125"/>
       <c r="E17" s="125"/>
       <c r="F17" s="125"/>
@@ -5615,10 +5744,10 @@
       <c r="Z17" s="125"/>
       <c r="AB17" s="93"/>
       <c r="AD17" s="125"/>
-      <c r="AE17" s="125"/>
-      <c r="AF17" s="92"/>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG17" s="125"/>
+      <c r="AH17" s="92"/>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C18" s="125"/>
       <c r="E18" s="125"/>
       <c r="F18" s="125"/>
@@ -5637,10 +5766,10 @@
       <c r="Z18" s="125"/>
       <c r="AB18" s="93"/>
       <c r="AD18" s="125"/>
-      <c r="AE18" s="125"/>
-      <c r="AF18" s="92"/>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG18" s="125"/>
+      <c r="AH18" s="92"/>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C19" s="125"/>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
@@ -5659,10 +5788,10 @@
       <c r="Z19" s="125"/>
       <c r="AB19" s="93"/>
       <c r="AD19" s="125"/>
-      <c r="AE19" s="125"/>
-      <c r="AF19" s="92"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG19" s="125"/>
+      <c r="AH19" s="92"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C20" s="125"/>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
@@ -5681,10 +5810,10 @@
       <c r="Z20" s="125"/>
       <c r="AB20" s="93"/>
       <c r="AD20" s="125"/>
-      <c r="AE20" s="125"/>
-      <c r="AF20" s="92"/>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG20" s="125"/>
+      <c r="AH20" s="92"/>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C21" s="125"/>
       <c r="E21" s="125"/>
       <c r="F21" s="125"/>
@@ -5703,10 +5832,10 @@
       <c r="Z21" s="125"/>
       <c r="AB21" s="93"/>
       <c r="AD21" s="125"/>
-      <c r="AE21" s="125"/>
-      <c r="AF21" s="92"/>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG21" s="125"/>
+      <c r="AH21" s="92"/>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C22" s="125"/>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -5725,10 +5854,10 @@
       <c r="Z22" s="125"/>
       <c r="AB22" s="93"/>
       <c r="AD22" s="125"/>
-      <c r="AE22" s="125"/>
-      <c r="AF22" s="92"/>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG22" s="125"/>
+      <c r="AH22" s="92"/>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C23" s="125"/>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -5747,10 +5876,10 @@
       <c r="Z23" s="125"/>
       <c r="AB23" s="93"/>
       <c r="AD23" s="125"/>
-      <c r="AE23" s="125"/>
-      <c r="AF23" s="92"/>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG23" s="125"/>
+      <c r="AH23" s="92"/>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C24" s="125"/>
       <c r="E24" s="125"/>
       <c r="F24" s="125"/>
@@ -5769,10 +5898,10 @@
       <c r="Z24" s="125"/>
       <c r="AB24" s="93"/>
       <c r="AD24" s="125"/>
-      <c r="AE24" s="125"/>
-      <c r="AF24" s="92"/>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG24" s="125"/>
+      <c r="AH24" s="92"/>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C25" s="125"/>
       <c r="E25" s="125"/>
       <c r="F25" s="125"/>
@@ -5791,10 +5920,10 @@
       <c r="Z25" s="125"/>
       <c r="AB25" s="93"/>
       <c r="AD25" s="125"/>
-      <c r="AE25" s="125"/>
-      <c r="AF25" s="92"/>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG25" s="125"/>
+      <c r="AH25" s="92"/>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C26" s="125"/>
       <c r="E26" s="125"/>
       <c r="F26" s="125"/>
@@ -5813,10 +5942,10 @@
       <c r="Z26" s="125"/>
       <c r="AB26" s="93"/>
       <c r="AD26" s="125"/>
-      <c r="AE26" s="125"/>
-      <c r="AF26" s="92"/>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG26" s="125"/>
+      <c r="AH26" s="92"/>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C27" s="125"/>
       <c r="E27" s="125"/>
       <c r="F27" s="125"/>
@@ -5835,10 +5964,10 @@
       <c r="Z27" s="125"/>
       <c r="AB27" s="93"/>
       <c r="AD27" s="125"/>
-      <c r="AE27" s="125"/>
-      <c r="AF27" s="92"/>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG27" s="125"/>
+      <c r="AH27" s="92"/>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C28" s="125"/>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
@@ -5857,10 +5986,10 @@
       <c r="Z28" s="125"/>
       <c r="AB28" s="93"/>
       <c r="AD28" s="125"/>
-      <c r="AE28" s="125"/>
-      <c r="AF28" s="92"/>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG28" s="125"/>
+      <c r="AH28" s="92"/>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C29" s="125"/>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
@@ -5879,10 +6008,10 @@
       <c r="Z29" s="125"/>
       <c r="AB29" s="93"/>
       <c r="AD29" s="125"/>
-      <c r="AE29" s="125"/>
-      <c r="AF29" s="92"/>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG29" s="125"/>
+      <c r="AH29" s="92"/>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C30" s="125"/>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -5901,10 +6030,10 @@
       <c r="Z30" s="125"/>
       <c r="AB30" s="93"/>
       <c r="AD30" s="125"/>
-      <c r="AE30" s="125"/>
-      <c r="AF30" s="92"/>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG30" s="125"/>
+      <c r="AH30" s="92"/>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C31" s="125"/>
       <c r="E31" s="125"/>
       <c r="F31" s="125"/>
@@ -5923,10 +6052,10 @@
       <c r="Z31" s="125"/>
       <c r="AB31" s="93"/>
       <c r="AD31" s="125"/>
-      <c r="AE31" s="125"/>
-      <c r="AF31" s="92"/>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG31" s="125"/>
+      <c r="AH31" s="92"/>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C32" s="125"/>
       <c r="E32" s="125"/>
       <c r="F32" s="125"/>
@@ -5945,10 +6074,10 @@
       <c r="Z32" s="125"/>
       <c r="AB32" s="93"/>
       <c r="AD32" s="125"/>
-      <c r="AE32" s="125"/>
-      <c r="AF32" s="92"/>
-    </row>
-    <row r="33" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG32" s="125"/>
+      <c r="AH32" s="92"/>
+    </row>
+    <row r="33" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C33" s="125"/>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
@@ -5967,10 +6096,10 @@
       <c r="Z33" s="125"/>
       <c r="AB33" s="93"/>
       <c r="AD33" s="125"/>
-      <c r="AE33" s="125"/>
-      <c r="AF33" s="92"/>
-    </row>
-    <row r="34" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG33" s="125"/>
+      <c r="AH33" s="92"/>
+    </row>
+    <row r="34" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C34" s="125"/>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
@@ -5989,10 +6118,10 @@
       <c r="Z34" s="125"/>
       <c r="AB34" s="93"/>
       <c r="AD34" s="125"/>
-      <c r="AE34" s="125"/>
-      <c r="AF34" s="92"/>
-    </row>
-    <row r="35" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG34" s="125"/>
+      <c r="AH34" s="92"/>
+    </row>
+    <row r="35" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C35" s="125"/>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
@@ -6011,10 +6140,10 @@
       <c r="Z35" s="125"/>
       <c r="AB35" s="93"/>
       <c r="AD35" s="125"/>
-      <c r="AE35" s="125"/>
-      <c r="AF35" s="92"/>
-    </row>
-    <row r="36" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG35" s="125"/>
+      <c r="AH35" s="92"/>
+    </row>
+    <row r="36" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C36" s="125"/>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
@@ -6033,10 +6162,10 @@
       <c r="Z36" s="125"/>
       <c r="AB36" s="93"/>
       <c r="AD36" s="125"/>
-      <c r="AE36" s="125"/>
-      <c r="AF36" s="92"/>
-    </row>
-    <row r="37" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG36" s="125"/>
+      <c r="AH36" s="92"/>
+    </row>
+    <row r="37" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C37" s="125"/>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -6055,10 +6184,10 @@
       <c r="Z37" s="125"/>
       <c r="AB37" s="93"/>
       <c r="AD37" s="125"/>
-      <c r="AE37" s="125"/>
-      <c r="AF37" s="92"/>
-    </row>
-    <row r="38" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG37" s="125"/>
+      <c r="AH37" s="92"/>
+    </row>
+    <row r="38" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C38" s="125"/>
       <c r="E38" s="125"/>
       <c r="F38" s="125"/>
@@ -6077,10 +6206,10 @@
       <c r="Z38" s="125"/>
       <c r="AB38" s="93"/>
       <c r="AD38" s="125"/>
-      <c r="AE38" s="125"/>
-      <c r="AF38" s="92"/>
-    </row>
-    <row r="39" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG38" s="125"/>
+      <c r="AH38" s="92"/>
+    </row>
+    <row r="39" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C39" s="125"/>
       <c r="E39" s="125"/>
       <c r="F39" s="125"/>
@@ -6099,10 +6228,10 @@
       <c r="Z39" s="125"/>
       <c r="AB39" s="93"/>
       <c r="AD39" s="125"/>
-      <c r="AE39" s="125"/>
-      <c r="AF39" s="92"/>
-    </row>
-    <row r="40" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG39" s="125"/>
+      <c r="AH39" s="92"/>
+    </row>
+    <row r="40" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C40" s="125"/>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
@@ -6121,10 +6250,10 @@
       <c r="Z40" s="125"/>
       <c r="AB40" s="93"/>
       <c r="AD40" s="125"/>
-      <c r="AE40" s="125"/>
-      <c r="AF40" s="92"/>
-    </row>
-    <row r="41" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG40" s="125"/>
+      <c r="AH40" s="92"/>
+    </row>
+    <row r="41" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C41" s="125"/>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -6143,10 +6272,10 @@
       <c r="Z41" s="125"/>
       <c r="AB41" s="93"/>
       <c r="AD41" s="125"/>
-      <c r="AE41" s="125"/>
-      <c r="AF41" s="92"/>
-    </row>
-    <row r="42" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG41" s="125"/>
+      <c r="AH41" s="92"/>
+    </row>
+    <row r="42" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C42" s="125"/>
       <c r="E42" s="125"/>
       <c r="F42" s="125"/>
@@ -6165,10 +6294,10 @@
       <c r="Z42" s="125"/>
       <c r="AB42" s="93"/>
       <c r="AD42" s="125"/>
-      <c r="AE42" s="125"/>
-      <c r="AF42" s="92"/>
-    </row>
-    <row r="43" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG42" s="125"/>
+      <c r="AH42" s="92"/>
+    </row>
+    <row r="43" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C43" s="125"/>
       <c r="E43" s="125"/>
       <c r="F43" s="125"/>
@@ -6187,10 +6316,10 @@
       <c r="Z43" s="125"/>
       <c r="AB43" s="93"/>
       <c r="AD43" s="125"/>
-      <c r="AE43" s="125"/>
-      <c r="AF43" s="92"/>
-    </row>
-    <row r="44" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG43" s="125"/>
+      <c r="AH43" s="92"/>
+    </row>
+    <row r="44" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C44" s="125"/>
       <c r="E44" s="125"/>
       <c r="F44" s="125"/>
@@ -6209,10 +6338,10 @@
       <c r="Z44" s="125"/>
       <c r="AB44" s="93"/>
       <c r="AD44" s="125"/>
-      <c r="AE44" s="125"/>
-      <c r="AF44" s="92"/>
-    </row>
-    <row r="45" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG44" s="125"/>
+      <c r="AH44" s="92"/>
+    </row>
+    <row r="45" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C45" s="125"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
@@ -6231,10 +6360,10 @@
       <c r="Z45" s="125"/>
       <c r="AB45" s="93"/>
       <c r="AD45" s="125"/>
-      <c r="AE45" s="125"/>
-      <c r="AF45" s="92"/>
-    </row>
-    <row r="46" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG45" s="125"/>
+      <c r="AH45" s="92"/>
+    </row>
+    <row r="46" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C46" s="125"/>
       <c r="E46" s="125"/>
       <c r="F46" s="125"/>
@@ -6253,10 +6382,10 @@
       <c r="Z46" s="125"/>
       <c r="AB46" s="93"/>
       <c r="AD46" s="125"/>
-      <c r="AE46" s="125"/>
-      <c r="AF46" s="92"/>
-    </row>
-    <row r="47" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG46" s="125"/>
+      <c r="AH46" s="92"/>
+    </row>
+    <row r="47" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C47" s="125"/>
       <c r="E47" s="125"/>
       <c r="F47" s="125"/>
@@ -6275,10 +6404,10 @@
       <c r="Z47" s="125"/>
       <c r="AB47" s="93"/>
       <c r="AD47" s="125"/>
-      <c r="AE47" s="125"/>
-      <c r="AF47" s="92"/>
-    </row>
-    <row r="48" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG47" s="125"/>
+      <c r="AH47" s="92"/>
+    </row>
+    <row r="48" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C48" s="125"/>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -6297,10 +6426,10 @@
       <c r="Z48" s="125"/>
       <c r="AB48" s="93"/>
       <c r="AD48" s="125"/>
-      <c r="AE48" s="125"/>
-      <c r="AF48" s="92"/>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG48" s="125"/>
+      <c r="AH48" s="92"/>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C49" s="125"/>
       <c r="E49" s="125"/>
       <c r="F49" s="125"/>
@@ -6319,10 +6448,10 @@
       <c r="Z49" s="125"/>
       <c r="AB49" s="93"/>
       <c r="AD49" s="125"/>
-      <c r="AE49" s="125"/>
-      <c r="AF49" s="92"/>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG49" s="125"/>
+      <c r="AH49" s="92"/>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C50" s="125"/>
       <c r="E50" s="125"/>
       <c r="F50" s="125"/>
@@ -6341,10 +6470,10 @@
       <c r="Z50" s="125"/>
       <c r="AB50" s="93"/>
       <c r="AD50" s="125"/>
-      <c r="AE50" s="125"/>
-      <c r="AF50" s="92"/>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG50" s="125"/>
+      <c r="AH50" s="92"/>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C51" s="125"/>
       <c r="E51" s="125"/>
       <c r="F51" s="125"/>
@@ -6363,10 +6492,10 @@
       <c r="Z51" s="125"/>
       <c r="AB51" s="93"/>
       <c r="AD51" s="125"/>
-      <c r="AE51" s="125"/>
-      <c r="AF51" s="92"/>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG51" s="125"/>
+      <c r="AH51" s="92"/>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C52" s="125"/>
       <c r="E52" s="125"/>
       <c r="F52" s="125"/>
@@ -6385,10 +6514,10 @@
       <c r="Z52" s="125"/>
       <c r="AB52" s="93"/>
       <c r="AD52" s="125"/>
-      <c r="AE52" s="125"/>
-      <c r="AF52" s="92"/>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG52" s="125"/>
+      <c r="AH52" s="92"/>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C53" s="125"/>
       <c r="E53" s="125"/>
       <c r="F53" s="125"/>
@@ -6407,10 +6536,10 @@
       <c r="Z53" s="125"/>
       <c r="AB53" s="93"/>
       <c r="AD53" s="125"/>
-      <c r="AE53" s="125"/>
-      <c r="AF53" s="92"/>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG53" s="125"/>
+      <c r="AH53" s="92"/>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C54" s="125"/>
       <c r="E54" s="125"/>
       <c r="F54" s="125"/>
@@ -6429,10 +6558,10 @@
       <c r="Z54" s="125"/>
       <c r="AB54" s="93"/>
       <c r="AD54" s="125"/>
-      <c r="AE54" s="125"/>
-      <c r="AF54" s="92"/>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG54" s="125"/>
+      <c r="AH54" s="92"/>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C55" s="125"/>
       <c r="E55" s="125"/>
       <c r="F55" s="125"/>
@@ -6451,10 +6580,10 @@
       <c r="Z55" s="125"/>
       <c r="AB55" s="93"/>
       <c r="AD55" s="125"/>
-      <c r="AE55" s="125"/>
-      <c r="AF55" s="92"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG55" s="125"/>
+      <c r="AH55" s="92"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C56" s="125"/>
       <c r="E56" s="125"/>
       <c r="F56" s="125"/>
@@ -6473,10 +6602,10 @@
       <c r="Z56" s="125"/>
       <c r="AB56" s="93"/>
       <c r="AD56" s="125"/>
-      <c r="AE56" s="125"/>
-      <c r="AF56" s="92"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG56" s="125"/>
+      <c r="AH56" s="92"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C57" s="125"/>
       <c r="E57" s="125"/>
       <c r="F57" s="125"/>
@@ -6495,10 +6624,10 @@
       <c r="Z57" s="125"/>
       <c r="AB57" s="93"/>
       <c r="AD57" s="125"/>
-      <c r="AE57" s="125"/>
-      <c r="AF57" s="92"/>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG57" s="125"/>
+      <c r="AH57" s="92"/>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C58" s="125"/>
       <c r="E58" s="125"/>
       <c r="F58" s="125"/>
@@ -6517,10 +6646,10 @@
       <c r="Z58" s="125"/>
       <c r="AB58" s="93"/>
       <c r="AD58" s="125"/>
-      <c r="AE58" s="125"/>
-      <c r="AF58" s="92"/>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG58" s="125"/>
+      <c r="AH58" s="92"/>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C59" s="125"/>
       <c r="E59" s="125"/>
       <c r="F59" s="125"/>
@@ -6539,10 +6668,10 @@
       <c r="Z59" s="125"/>
       <c r="AB59" s="93"/>
       <c r="AD59" s="125"/>
-      <c r="AE59" s="125"/>
-      <c r="AF59" s="92"/>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG59" s="125"/>
+      <c r="AH59" s="92"/>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C60" s="125"/>
       <c r="E60" s="125"/>
       <c r="F60" s="125"/>
@@ -6561,10 +6690,10 @@
       <c r="Z60" s="125"/>
       <c r="AB60" s="93"/>
       <c r="AD60" s="125"/>
-      <c r="AE60" s="125"/>
-      <c r="AF60" s="92"/>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG60" s="125"/>
+      <c r="AH60" s="92"/>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C61" s="125"/>
       <c r="E61" s="125"/>
       <c r="F61" s="125"/>
@@ -6583,10 +6712,10 @@
       <c r="Z61" s="125"/>
       <c r="AB61" s="93"/>
       <c r="AD61" s="125"/>
-      <c r="AE61" s="125"/>
-      <c r="AF61" s="92"/>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG61" s="125"/>
+      <c r="AH61" s="92"/>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C62" s="125"/>
       <c r="E62" s="125"/>
       <c r="F62" s="125"/>
@@ -6605,10 +6734,10 @@
       <c r="Z62" s="125"/>
       <c r="AB62" s="93"/>
       <c r="AD62" s="125"/>
-      <c r="AE62" s="125"/>
-      <c r="AF62" s="92"/>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG62" s="125"/>
+      <c r="AH62" s="92"/>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C63" s="125"/>
       <c r="E63" s="125"/>
       <c r="F63" s="125"/>
@@ -6627,10 +6756,10 @@
       <c r="Z63" s="125"/>
       <c r="AB63" s="93"/>
       <c r="AD63" s="125"/>
-      <c r="AE63" s="125"/>
-      <c r="AF63" s="92"/>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG63" s="125"/>
+      <c r="AH63" s="92"/>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C64" s="125"/>
       <c r="E64" s="125"/>
       <c r="F64" s="125"/>
@@ -6649,10 +6778,10 @@
       <c r="Z64" s="125"/>
       <c r="AB64" s="93"/>
       <c r="AD64" s="125"/>
-      <c r="AE64" s="125"/>
-      <c r="AF64" s="92"/>
-    </row>
-    <row r="65" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG64" s="125"/>
+      <c r="AH64" s="92"/>
+    </row>
+    <row r="65" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C65" s="125"/>
       <c r="E65" s="125"/>
       <c r="F65" s="125"/>
@@ -6671,10 +6800,10 @@
       <c r="Z65" s="125"/>
       <c r="AB65" s="93"/>
       <c r="AD65" s="125"/>
-      <c r="AE65" s="125"/>
-      <c r="AF65" s="92"/>
-    </row>
-    <row r="66" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG65" s="125"/>
+      <c r="AH65" s="92"/>
+    </row>
+    <row r="66" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C66" s="125"/>
       <c r="E66" s="125"/>
       <c r="F66" s="125"/>
@@ -6693,10 +6822,10 @@
       <c r="Z66" s="125"/>
       <c r="AB66" s="93"/>
       <c r="AD66" s="125"/>
-      <c r="AE66" s="125"/>
-      <c r="AF66" s="92"/>
-    </row>
-    <row r="67" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG66" s="125"/>
+      <c r="AH66" s="92"/>
+    </row>
+    <row r="67" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C67" s="125"/>
       <c r="E67" s="125"/>
       <c r="F67" s="125"/>
@@ -6715,10 +6844,10 @@
       <c r="Z67" s="125"/>
       <c r="AB67" s="93"/>
       <c r="AD67" s="125"/>
-      <c r="AE67" s="125"/>
-      <c r="AF67" s="92"/>
-    </row>
-    <row r="68" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG67" s="125"/>
+      <c r="AH67" s="92"/>
+    </row>
+    <row r="68" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C68" s="125"/>
       <c r="E68" s="125"/>
       <c r="F68" s="125"/>
@@ -6737,10 +6866,10 @@
       <c r="Z68" s="125"/>
       <c r="AB68" s="93"/>
       <c r="AD68" s="125"/>
-      <c r="AE68" s="125"/>
-      <c r="AF68" s="92"/>
-    </row>
-    <row r="69" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG68" s="125"/>
+      <c r="AH68" s="92"/>
+    </row>
+    <row r="69" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C69" s="125"/>
       <c r="E69" s="125"/>
       <c r="F69" s="125"/>
@@ -6759,10 +6888,10 @@
       <c r="Z69" s="125"/>
       <c r="AB69" s="93"/>
       <c r="AD69" s="125"/>
-      <c r="AE69" s="125"/>
-      <c r="AF69" s="92"/>
-    </row>
-    <row r="70" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG69" s="125"/>
+      <c r="AH69" s="92"/>
+    </row>
+    <row r="70" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C70" s="125"/>
       <c r="E70" s="125"/>
       <c r="F70" s="125"/>
@@ -6781,10 +6910,10 @@
       <c r="Z70" s="125"/>
       <c r="AB70" s="93"/>
       <c r="AD70" s="125"/>
-      <c r="AE70" s="125"/>
-      <c r="AF70" s="92"/>
-    </row>
-    <row r="71" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG70" s="125"/>
+      <c r="AH70" s="92"/>
+    </row>
+    <row r="71" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C71" s="125"/>
       <c r="E71" s="125"/>
       <c r="F71" s="125"/>
@@ -6803,10 +6932,10 @@
       <c r="Z71" s="125"/>
       <c r="AB71" s="93"/>
       <c r="AD71" s="125"/>
-      <c r="AE71" s="125"/>
-      <c r="AF71" s="92"/>
-    </row>
-    <row r="72" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG71" s="125"/>
+      <c r="AH71" s="92"/>
+    </row>
+    <row r="72" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C72" s="125"/>
       <c r="E72" s="125"/>
       <c r="F72" s="125"/>
@@ -6825,10 +6954,10 @@
       <c r="Z72" s="125"/>
       <c r="AB72" s="93"/>
       <c r="AD72" s="125"/>
-      <c r="AE72" s="125"/>
-      <c r="AF72" s="92"/>
-    </row>
-    <row r="73" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG72" s="125"/>
+      <c r="AH72" s="92"/>
+    </row>
+    <row r="73" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C73" s="125"/>
       <c r="E73" s="125"/>
       <c r="F73" s="125"/>
@@ -6847,10 +6976,10 @@
       <c r="Z73" s="125"/>
       <c r="AB73" s="93"/>
       <c r="AD73" s="125"/>
-      <c r="AE73" s="125"/>
-      <c r="AF73" s="92"/>
-    </row>
-    <row r="74" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG73" s="125"/>
+      <c r="AH73" s="92"/>
+    </row>
+    <row r="74" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C74" s="125"/>
       <c r="E74" s="125"/>
       <c r="F74" s="125"/>
@@ -6869,10 +6998,10 @@
       <c r="Z74" s="125"/>
       <c r="AB74" s="93"/>
       <c r="AD74" s="125"/>
-      <c r="AE74" s="125"/>
-      <c r="AF74" s="92"/>
-    </row>
-    <row r="75" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG74" s="125"/>
+      <c r="AH74" s="92"/>
+    </row>
+    <row r="75" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C75" s="125"/>
       <c r="E75" s="125"/>
       <c r="F75" s="125"/>
@@ -6891,10 +7020,10 @@
       <c r="Z75" s="125"/>
       <c r="AB75" s="93"/>
       <c r="AD75" s="125"/>
-      <c r="AE75" s="125"/>
-      <c r="AF75" s="92"/>
-    </row>
-    <row r="76" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG75" s="125"/>
+      <c r="AH75" s="92"/>
+    </row>
+    <row r="76" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C76" s="125"/>
       <c r="E76" s="125"/>
       <c r="F76" s="125"/>
@@ -6913,10 +7042,10 @@
       <c r="Z76" s="125"/>
       <c r="AB76" s="93"/>
       <c r="AD76" s="125"/>
-      <c r="AE76" s="125"/>
-      <c r="AF76" s="92"/>
-    </row>
-    <row r="77" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG76" s="125"/>
+      <c r="AH76" s="92"/>
+    </row>
+    <row r="77" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C77" s="125"/>
       <c r="E77" s="125"/>
       <c r="F77" s="125"/>
@@ -6935,10 +7064,10 @@
       <c r="Z77" s="125"/>
       <c r="AB77" s="93"/>
       <c r="AD77" s="125"/>
-      <c r="AE77" s="125"/>
-      <c r="AF77" s="92"/>
-    </row>
-    <row r="78" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG77" s="125"/>
+      <c r="AH77" s="92"/>
+    </row>
+    <row r="78" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C78" s="125"/>
       <c r="E78" s="125"/>
       <c r="F78" s="125"/>
@@ -6957,10 +7086,10 @@
       <c r="Z78" s="125"/>
       <c r="AB78" s="93"/>
       <c r="AD78" s="125"/>
-      <c r="AE78" s="125"/>
-      <c r="AF78" s="92"/>
-    </row>
-    <row r="79" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG78" s="125"/>
+      <c r="AH78" s="92"/>
+    </row>
+    <row r="79" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C79" s="125"/>
       <c r="E79" s="125"/>
       <c r="F79" s="125"/>
@@ -6979,10 +7108,10 @@
       <c r="Z79" s="125"/>
       <c r="AB79" s="93"/>
       <c r="AD79" s="125"/>
-      <c r="AE79" s="125"/>
-      <c r="AF79" s="92"/>
-    </row>
-    <row r="80" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG79" s="125"/>
+      <c r="AH79" s="92"/>
+    </row>
+    <row r="80" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C80" s="125"/>
       <c r="E80" s="125"/>
       <c r="F80" s="125"/>
@@ -7001,10 +7130,10 @@
       <c r="Z80" s="125"/>
       <c r="AB80" s="93"/>
       <c r="AD80" s="125"/>
-      <c r="AE80" s="125"/>
-      <c r="AF80" s="92"/>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG80" s="125"/>
+      <c r="AH80" s="92"/>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C81" s="125"/>
       <c r="E81" s="125"/>
       <c r="F81" s="125"/>
@@ -7023,10 +7152,10 @@
       <c r="Z81" s="125"/>
       <c r="AB81" s="93"/>
       <c r="AD81" s="125"/>
-      <c r="AE81" s="125"/>
-      <c r="AF81" s="92"/>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG81" s="125"/>
+      <c r="AH81" s="92"/>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C82" s="125"/>
       <c r="E82" s="125"/>
       <c r="F82" s="125"/>
@@ -7045,10 +7174,10 @@
       <c r="Z82" s="125"/>
       <c r="AB82" s="93"/>
       <c r="AD82" s="125"/>
-      <c r="AE82" s="125"/>
-      <c r="AF82" s="92"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG82" s="125"/>
+      <c r="AH82" s="92"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C83" s="125"/>
       <c r="E83" s="125"/>
       <c r="F83" s="125"/>
@@ -7067,10 +7196,10 @@
       <c r="Z83" s="125"/>
       <c r="AB83" s="93"/>
       <c r="AD83" s="125"/>
-      <c r="AE83" s="125"/>
-      <c r="AF83" s="92"/>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG83" s="125"/>
+      <c r="AH83" s="92"/>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C84" s="125"/>
       <c r="E84" s="125"/>
       <c r="F84" s="125"/>
@@ -7089,10 +7218,10 @@
       <c r="Z84" s="125"/>
       <c r="AB84" s="93"/>
       <c r="AD84" s="125"/>
-      <c r="AE84" s="125"/>
-      <c r="AF84" s="92"/>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG84" s="125"/>
+      <c r="AH84" s="92"/>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C85" s="125"/>
       <c r="E85" s="125"/>
       <c r="F85" s="125"/>
@@ -7111,10 +7240,10 @@
       <c r="Z85" s="125"/>
       <c r="AB85" s="93"/>
       <c r="AD85" s="125"/>
-      <c r="AE85" s="125"/>
-      <c r="AF85" s="92"/>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG85" s="125"/>
+      <c r="AH85" s="92"/>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C86" s="125"/>
       <c r="E86" s="125"/>
       <c r="F86" s="125"/>
@@ -7133,10 +7262,10 @@
       <c r="Z86" s="125"/>
       <c r="AB86" s="93"/>
       <c r="AD86" s="125"/>
-      <c r="AE86" s="125"/>
-      <c r="AF86" s="92"/>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG86" s="125"/>
+      <c r="AH86" s="92"/>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C87" s="125"/>
       <c r="E87" s="125"/>
       <c r="F87" s="125"/>
@@ -7155,10 +7284,10 @@
       <c r="Z87" s="125"/>
       <c r="AB87" s="93"/>
       <c r="AD87" s="125"/>
-      <c r="AE87" s="125"/>
-      <c r="AF87" s="92"/>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG87" s="125"/>
+      <c r="AH87" s="92"/>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C88" s="125"/>
       <c r="E88" s="125"/>
       <c r="F88" s="125"/>
@@ -7177,10 +7306,10 @@
       <c r="Z88" s="125"/>
       <c r="AB88" s="93"/>
       <c r="AD88" s="125"/>
-      <c r="AE88" s="125"/>
-      <c r="AF88" s="92"/>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG88" s="125"/>
+      <c r="AH88" s="92"/>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C89" s="125"/>
       <c r="E89" s="125"/>
       <c r="F89" s="125"/>
@@ -7199,10 +7328,10 @@
       <c r="Z89" s="125"/>
       <c r="AB89" s="93"/>
       <c r="AD89" s="125"/>
-      <c r="AE89" s="125"/>
-      <c r="AF89" s="92"/>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG89" s="125"/>
+      <c r="AH89" s="92"/>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C90" s="125"/>
       <c r="E90" s="125"/>
       <c r="F90" s="125"/>
@@ -7221,10 +7350,10 @@
       <c r="Z90" s="125"/>
       <c r="AB90" s="93"/>
       <c r="AD90" s="125"/>
-      <c r="AE90" s="125"/>
-      <c r="AF90" s="92"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG90" s="125"/>
+      <c r="AH90" s="92"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C91" s="125"/>
       <c r="E91" s="125"/>
       <c r="F91" s="125"/>
@@ -7243,10 +7372,10 @@
       <c r="Z91" s="125"/>
       <c r="AB91" s="93"/>
       <c r="AD91" s="125"/>
-      <c r="AE91" s="125"/>
-      <c r="AF91" s="92"/>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="AG91" s="125"/>
+      <c r="AH91" s="92"/>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C92" s="125"/>
       <c r="E92" s="125"/>
       <c r="F92" s="125"/>
@@ -7265,8 +7394,8 @@
       <c r="Z92" s="125"/>
       <c r="AB92" s="93"/>
       <c r="AD92" s="125"/>
-      <c r="AE92" s="125"/>
-      <c r="AF92" s="92"/>
+      <c r="AG92" s="125"/>
+      <c r="AH92" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7277,22 +7406,19 @@
     <mergeCell ref="AE2:AH2"/>
   </mergeCells>
   <conditionalFormatting sqref="O4:O92">
-    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:P92">
-    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q4">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="D4:D92" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Private Car,Two Wheeler,Commercial Vehicle,Taxi"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E4:E92 C4" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C4 E4:E92" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Individual,Company,Taxi,Government"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7311,241 +7437,241 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="135" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
+      <c r="A1" s="140" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C7" s="127" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C8" s="127" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C9" s="127" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C10" s="127" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C11" s="127" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C12" s="127" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C13" s="127" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C14" s="127" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C15" s="127" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C16" s="127" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C17" s="127" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="C18" s="127" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="128" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="B19" s="129" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C19" s="130" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="128" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="B20" s="129" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C20" s="130" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="128" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="B21" s="129" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C21" s="130" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="128" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="B22" s="129" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C22" s="130" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -7558,7 +7684,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G271"/>
+  <dimension ref="A1:G279"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -7571,5200 +7697,5368 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="136" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
+      <c r="A1" s="141" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
     </row>
     <row r="2" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="13" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F13" s="14"/>
       <c r="G13" s="14" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="14" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F15" s="14"/>
       <c r="G15" s="14" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F18" s="14"/>
       <c r="G18" s="14" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F19" s="15"/>
       <c r="G19" s="15" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F20" s="16"/>
       <c r="G20" s="16" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F21" s="16"/>
       <c r="G21" s="16" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F22" s="17"/>
       <c r="G22" s="17" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F23" s="17"/>
       <c r="G23" s="17" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F24" s="17"/>
       <c r="G24" s="17" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F25" s="18"/>
       <c r="G25" s="18" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F26" s="19"/>
       <c r="G26" s="19" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F27" s="20"/>
       <c r="G27" s="20" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F28" s="21"/>
       <c r="G28" s="21" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="22" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D29" s="22"/>
       <c r="E29" s="22" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="B30" s="22"/>
       <c r="C30" s="22" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="22" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D31" s="28"/>
       <c r="E31" s="28" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="G31" s="28" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F32" s="29"/>
       <c r="G32" s="29" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="30" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="B33" s="30"/>
       <c r="C33" s="30" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D33" s="30"/>
       <c r="E33" s="30" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="F33" s="30" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="G33" s="30" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="31" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="B34" s="31"/>
       <c r="C34" s="31" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D34" s="31"/>
       <c r="E34" s="31" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="G34" s="31" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="32" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="B35" s="32"/>
       <c r="C35" s="32" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="E35" s="32" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F35" s="32"/>
       <c r="G35" s="32" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="33" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="B36" s="33"/>
       <c r="C36" s="33" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="E36" s="33" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F36" s="33"/>
       <c r="G36" s="33" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="34" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="B37" s="34"/>
       <c r="C37" s="34" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D37" s="34" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="E37" s="34" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F37" s="34"/>
       <c r="G37" s="34" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="35" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="B38" s="35"/>
       <c r="C38" s="35" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D38" s="35" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="E38" s="35" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F38" s="35"/>
       <c r="G38" s="35" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="36" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="B39" s="36"/>
       <c r="C39" s="36" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D39" s="36"/>
       <c r="E39" s="36" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="37" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="B40" s="37"/>
       <c r="C40" s="37" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F40" s="37"/>
       <c r="G40" s="37" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="38" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="B41" s="38"/>
       <c r="C41" s="38" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F41" s="38"/>
       <c r="G41" s="38" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="39" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="B42" s="39"/>
       <c r="C42" s="39" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D42" s="39"/>
       <c r="E42" s="39" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="F42" s="39" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="G42" s="39" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="40" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="B43" s="40"/>
       <c r="C43" s="40" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F43" s="40"/>
       <c r="G43" s="40" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="41" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="B44" s="41"/>
       <c r="C44" s="41" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D44" s="41" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="E44" s="41" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F44" s="41"/>
       <c r="G44" s="41" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="41" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="B45" s="41"/>
       <c r="C45" s="41" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D45" s="41" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="E45" s="41" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F45" s="41"/>
       <c r="G45" s="41" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="42" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="B46" s="42"/>
       <c r="C46" s="42" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D46" s="42" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="E46" s="42" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F46" s="42"/>
       <c r="G46" s="42" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="42" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="B47" s="42"/>
       <c r="C47" s="42" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D47" s="42" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="E47" s="42" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F47" s="42"/>
       <c r="G47" s="42" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="42" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="42" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D48" s="42" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="E48" s="42" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F48" s="42"/>
       <c r="G48" s="42" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="43" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="B49" s="43"/>
       <c r="C49" s="43" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D49" s="43" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="E49" s="43" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F49" s="43"/>
       <c r="G49" s="43" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="43" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="B50" s="43"/>
       <c r="C50" s="43" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D50" s="43" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="E50" s="43" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F50" s="43"/>
       <c r="G50" s="43" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="45" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="B51" s="45"/>
       <c r="C51" s="45" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D51" s="45" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="E51" s="45" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F51" s="45"/>
       <c r="G51" s="45" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="45" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="B52" s="45"/>
       <c r="C52" s="45" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D52" s="45" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="E52" s="45" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F52" s="45"/>
       <c r="G52" s="45" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="46" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="B53" s="46"/>
       <c r="C53" s="46" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D53" s="46" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="E53" s="46" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F53" s="46"/>
       <c r="G53" s="46" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="47" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="B54" s="47"/>
       <c r="C54" s="47" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D54" s="47" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="E54" s="47" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F54" s="47"/>
       <c r="G54" s="47" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="47" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="B55" s="47"/>
       <c r="C55" s="47" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D55" s="47" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="E55" s="47" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F55" s="47"/>
       <c r="G55" s="47" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="48" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="B56" s="48"/>
       <c r="C56" s="48" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D56" s="48" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="E56" s="48" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F56" s="48"/>
       <c r="G56" s="48" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="48" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="B57" s="48"/>
       <c r="C57" s="48" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D57" s="48" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="E57" s="48" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F57" s="48"/>
       <c r="G57" s="48" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="48" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="B58" s="48"/>
       <c r="C58" s="48" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D58" s="48" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="E58" s="48" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F58" s="48"/>
       <c r="G58" s="48" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="48" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="B59" s="48"/>
       <c r="C59" s="48" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D59" s="48" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="E59" s="48" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F59" s="48"/>
       <c r="G59" s="48" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="48" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="B60" s="48"/>
       <c r="C60" s="48" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D60" s="48" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="E60" s="48" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F60" s="48"/>
       <c r="G60" s="48" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="49" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="B61" s="49"/>
       <c r="C61" s="49" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D61" s="49" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="E61" s="49" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F61" s="49"/>
       <c r="G61" s="49" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="49" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="B62" s="49"/>
       <c r="C62" s="49" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D62" s="49" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="E62" s="49" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F62" s="49"/>
       <c r="G62" s="49" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="49" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="B63" s="49"/>
       <c r="C63" s="49" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D63" s="49" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="E63" s="49" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F63" s="49"/>
       <c r="G63" s="49" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="49" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="B64" s="49"/>
       <c r="C64" s="49" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="E64" s="49" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F64" s="49"/>
       <c r="G64" s="49" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="49" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="B65" s="49"/>
       <c r="C65" s="49" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="E65" s="49" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F65" s="49"/>
       <c r="G65" s="49" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="49" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="B66" s="49"/>
       <c r="C66" s="49" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D66" s="49" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="E66" s="49" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F66" s="49"/>
       <c r="G66" s="49" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="49" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="B67" s="49"/>
       <c r="C67" s="49" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D67" s="49" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="E67" s="49" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F67" s="49"/>
       <c r="G67" s="49" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="49" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="B68" s="49"/>
       <c r="C68" s="49" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D68" s="49" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E68" s="49" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F68" s="49"/>
       <c r="G68" s="49" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="50" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="B69" s="50"/>
       <c r="C69" s="50" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D69" s="50" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F69" s="50"/>
       <c r="G69" s="50" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="50" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="B70" s="50"/>
       <c r="C70" s="50" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D70" s="50" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F70" s="50"/>
       <c r="G70" s="50" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="50" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="B71" s="50"/>
       <c r="C71" s="50" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D71" s="50" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F71" s="50"/>
       <c r="G71" s="50" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="51" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B72" s="51"/>
       <c r="C72" s="51" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D72" s="51" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="E72" s="51" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F72" s="51"/>
       <c r="G72" s="51" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="51" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="B73" s="51"/>
       <c r="C73" s="51" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D73" s="51" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="E73" s="51" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F73" s="51"/>
       <c r="G73" s="51" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="51" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="B74" s="51"/>
       <c r="C74" s="51" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D74" s="51" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="E74" s="51" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F74" s="51"/>
       <c r="G74" s="51" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="51" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="B75" s="51"/>
       <c r="C75" s="51" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D75" s="51" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="E75" s="51" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F75" s="51"/>
       <c r="G75" s="51" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="52" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="B76" s="52"/>
       <c r="C76" s="52" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D76" s="52" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="E76" s="52" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F76" s="52"/>
       <c r="G76" s="52" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="52" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="B77" s="52"/>
       <c r="C77" s="52" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D77" s="52" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="E77" s="52" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F77" s="52"/>
       <c r="G77" s="52" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="52" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="B78" s="52"/>
       <c r="C78" s="52" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D78" s="52" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="E78" s="52" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F78" s="52"/>
       <c r="G78" s="52" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="53" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="B79" s="53"/>
       <c r="C79" s="53" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D79" s="53" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="E79" s="53" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F79" s="53"/>
       <c r="G79" s="53" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="54" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="B80" s="54"/>
       <c r="C80" s="54" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D80" s="54" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="E80" s="54" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F80" s="54"/>
       <c r="G80" s="54" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="55" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="B81" s="55"/>
       <c r="C81" s="55" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D81" s="55" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="E81" s="55" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F81" s="55"/>
       <c r="G81" s="55" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="55" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="B82" s="55"/>
       <c r="C82" s="55" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D82" s="55" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="E82" s="55" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F82" s="55"/>
       <c r="G82" s="55" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="57" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="B83" s="57"/>
       <c r="C83" s="57" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D83" s="57" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="E83" s="57" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F83" s="57"/>
       <c r="G83" s="57" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="59" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="B84" s="59"/>
       <c r="C84" s="59" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D84" s="59" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="E84" s="59" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F84" s="59"/>
       <c r="G84" s="59" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="60" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="B85" s="60"/>
       <c r="C85" s="60" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D85" s="60" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="E85" s="60" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="F85" s="60"/>
       <c r="G85" s="60" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="61" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="B86" s="61"/>
       <c r="C86" s="61" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D86" s="61" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="E86" s="61" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F86" s="61"/>
       <c r="G86" s="61" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="62" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="B87" s="62"/>
       <c r="C87" s="62" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D87" s="62" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="E87" s="62" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F87" s="62"/>
       <c r="G87" s="62" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="63" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="B88" s="63"/>
       <c r="C88" s="63" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D88" s="63" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="E88" s="63" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F88" s="63" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="G88" s="63" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="64" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B89" s="64"/>
       <c r="C89" s="64" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D89" s="64" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="E89" s="64" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F89" s="64"/>
       <c r="G89" s="64" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="65" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="B90" s="65"/>
       <c r="C90" s="65" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D90" s="65" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="E90" s="65" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F90" s="65"/>
       <c r="G90" s="65" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="65" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="B91" s="65"/>
       <c r="C91" s="65" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D91" s="65" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="E91" s="65" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F91" s="65"/>
       <c r="G91" s="65" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="65" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="B92" s="65"/>
       <c r="C92" s="65" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D92" s="65" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="E92" s="65" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F92" s="65"/>
       <c r="G92" s="65" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="66" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="B93" s="66"/>
       <c r="C93" s="66" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D93" s="66" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="E93" s="66" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F93" s="66"/>
       <c r="G93" s="66" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="67" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="B94" s="67"/>
       <c r="C94" s="67" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D94" s="67" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="E94" s="67" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F94" s="67"/>
       <c r="G94" s="67" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="67" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="B95" s="67"/>
       <c r="C95" s="67" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D95" s="67" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="E95" s="67" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F95" s="67"/>
       <c r="G95" s="67" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="67" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="B96" s="67"/>
       <c r="C96" s="67" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D96" s="67" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="E96" s="67" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F96" s="67"/>
       <c r="G96" s="67" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="67" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="B97" s="67"/>
       <c r="C97" s="67" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D97" s="67" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="E97" s="67" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F97" s="67"/>
       <c r="G97" s="67" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="67" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="B98" s="67"/>
       <c r="C98" s="67" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D98" s="67" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E98" s="67" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F98" s="67"/>
       <c r="G98" s="67" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="67" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="B99" s="67"/>
       <c r="C99" s="67" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D99" s="67" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="E99" s="67" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F99" s="67"/>
       <c r="G99" s="67" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="68" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="B100" s="68"/>
       <c r="C100" s="68" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D100" s="68" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="E100" s="68" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F100" s="68"/>
       <c r="G100" s="68" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="69" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="B101" s="69"/>
       <c r="C101" s="69" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D101" s="69" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="E101" s="69" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F101" s="69"/>
       <c r="G101" s="69" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="69" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="B102" s="69"/>
       <c r="C102" s="69" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D102" s="69" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="E102" s="69" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F102" s="69"/>
       <c r="G102" s="69" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="70" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="B103" s="70"/>
       <c r="C103" s="70" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D103" s="70" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="E103" s="70" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F103" s="70"/>
       <c r="G103" s="70" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="70" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="B104" s="70"/>
       <c r="C104" s="70" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D104" s="70" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="E104" s="70" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F104" s="70"/>
       <c r="G104" s="70" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="70" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="B105" s="70"/>
       <c r="C105" s="70" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D105" s="70" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="E105" s="70" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F105" s="70"/>
       <c r="G105" s="70" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="71" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="B106" s="71"/>
       <c r="C106" s="71" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D106" s="71" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="E106" s="71" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F106" s="71"/>
       <c r="G106" s="71" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="72" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="B107" s="72"/>
       <c r="C107" s="72" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D107" s="72" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="E107" s="72" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F107" s="72"/>
       <c r="G107" s="72" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="73" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="B108" s="73"/>
       <c r="C108" s="73" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D108" s="73" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="E108" s="73" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F108" s="73"/>
       <c r="G108" s="73" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="74" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="B109" s="74"/>
       <c r="C109" s="74" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D109" s="74" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="E109" s="74" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F109" s="74"/>
       <c r="G109" s="74" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="74" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="B110" s="74"/>
       <c r="C110" s="74" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D110" s="74" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="E110" s="74" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F110" s="74"/>
       <c r="G110" s="74" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="75" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="B111" s="75"/>
       <c r="C111" s="75" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D111" s="75" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="E111" s="75" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F111" s="75"/>
       <c r="G111" s="75" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="76" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="B112" s="76"/>
       <c r="C112" s="76" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D112" s="76" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="E112" s="76" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F112" s="76"/>
       <c r="G112" s="76" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="77" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="B113" s="77"/>
       <c r="C113" s="77" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D113" s="77" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="E113" s="77" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F113" s="77"/>
       <c r="G113" s="77" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="77" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="B114" s="77"/>
       <c r="C114" s="77" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D114" s="77" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="E114" s="77" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F114" s="77"/>
       <c r="G114" s="77" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="78" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="B115" s="78"/>
       <c r="C115" s="78" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D115" s="78" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="E115" s="78" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F115" s="78"/>
       <c r="G115" s="78" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="78" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="B116" s="78"/>
       <c r="C116" s="78" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D116" s="78" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="E116" s="78" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F116" s="78"/>
       <c r="G116" s="78" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="78" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="B117" s="78"/>
       <c r="C117" s="78" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D117" s="78" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="E117" s="78" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="F117" s="78"/>
       <c r="G117" s="78" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="79" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="B118" s="79"/>
       <c r="C118" s="79" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D118" s="79" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="E118" s="79" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F118" s="79"/>
       <c r="G118" s="79" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="80" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="B119" s="80"/>
       <c r="C119" s="80" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D119" s="80" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="E119" s="80" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F119" s="80"/>
       <c r="G119" s="80" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="80" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="B120" s="80"/>
       <c r="C120" s="80" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D120" s="80" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="E120" s="80" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F120" s="80"/>
       <c r="G120" s="80" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="80" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="B121" s="80"/>
       <c r="C121" s="80" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D121" s="80" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="E121" s="80" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F121" s="80"/>
       <c r="G121" s="80" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="81" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="B122" s="81"/>
       <c r="C122" s="81" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D122" s="81" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="E122" s="81" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="F122" s="81" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="G122" s="81" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="82" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="B123" s="82"/>
       <c r="C123" s="82" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D123" s="82" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="E123" s="82" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F123" s="82"/>
       <c r="G123" s="82" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="82" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="B124" s="82"/>
       <c r="C124" s="82" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D124" s="82" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="E124" s="82" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F124" s="82"/>
       <c r="G124" s="82" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="82" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="B125" s="82"/>
       <c r="C125" s="82" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D125" s="82" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="E125" s="82" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F125" s="82"/>
       <c r="G125" s="82" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="82" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="B126" s="82"/>
       <c r="C126" s="82" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D126" s="82" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="E126" s="82" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F126" s="82"/>
       <c r="G126" s="82" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="82" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="B127" s="82"/>
       <c r="C127" s="82" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D127" s="82" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="E127" s="82" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F127" s="82"/>
       <c r="G127" s="82" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="82" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="B128" s="82"/>
       <c r="C128" s="82" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D128" s="82" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="E128" s="82" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F128" s="82"/>
       <c r="G128" s="82" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="83" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="B129" s="83"/>
       <c r="C129" s="83" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D129" s="83" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="E129" s="83" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F129" s="83"/>
       <c r="G129" s="83" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="84" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="B130" s="84"/>
       <c r="C130" s="84" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D130" s="84" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="E130" s="84" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F130" s="84"/>
       <c r="G130" s="84" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="84" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="B131" s="84"/>
       <c r="C131" s="84" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D131" s="84" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="E131" s="84" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F131" s="84"/>
       <c r="G131" s="84" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="84" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="B132" s="84"/>
       <c r="C132" s="84" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D132" s="84" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="E132" s="84" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F132" s="84"/>
       <c r="G132" s="84" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="84" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="B133" s="84"/>
       <c r="C133" s="84" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D133" s="84" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="E133" s="84" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F133" s="84"/>
       <c r="G133" s="84" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="84" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="B134" s="84"/>
       <c r="C134" s="84" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D134" s="84" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="E134" s="84" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F134" s="84"/>
       <c r="G134" s="84" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="85" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="B135" s="85"/>
       <c r="C135" s="85" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D135" s="85" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="E135" s="85" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F135" s="85"/>
       <c r="G135" s="85" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="85" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="B136" s="85"/>
       <c r="C136" s="85" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D136" s="85" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="E136" s="85" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F136" s="85"/>
       <c r="G136" s="85" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="85" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="B137" s="85"/>
       <c r="C137" s="85" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D137" s="85" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="E137" s="85" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F137" s="85"/>
       <c r="G137" s="85" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="85" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="B138" s="85"/>
       <c r="C138" s="85" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D138" s="85" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="E138" s="85" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F138" s="85"/>
       <c r="G138" s="85" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="85" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="B139" s="85"/>
       <c r="C139" s="85" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D139" s="85" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="E139" s="85" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F139" s="85"/>
       <c r="G139" s="85" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="85" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="B140" s="85"/>
       <c r="C140" s="85" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D140" s="85" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="E140" s="85" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F140" s="85"/>
       <c r="G140" s="85" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="85" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="B141" s="85"/>
       <c r="C141" s="85" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D141" s="85" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="E141" s="85" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F141" s="85"/>
       <c r="G141" s="85" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="85" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="B142" s="85"/>
       <c r="C142" s="85" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D142" s="85" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="E142" s="85" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F142" s="85"/>
       <c r="G142" s="85" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="85" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="B143" s="85"/>
       <c r="C143" s="85" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D143" s="85" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="E143" s="85" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F143" s="85"/>
       <c r="G143" s="85" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="86" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="B144" s="86"/>
       <c r="C144" s="86" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D144" s="86"/>
       <c r="E144" s="86" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F144" s="86"/>
       <c r="G144" s="86" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="86" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="B145" s="86"/>
       <c r="C145" s="86" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D145" s="86" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="E145" s="86" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F145" s="86"/>
       <c r="G145" s="86" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="86" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="B146" s="86"/>
       <c r="C146" s="86" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D146" s="86" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="E146" s="86" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F146" s="86"/>
       <c r="G146" s="86" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="86" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="B147" s="86"/>
       <c r="C147" s="86" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D147" s="86" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="E147" s="86" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F147" s="86"/>
       <c r="G147" s="86" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="86" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="B148" s="86"/>
       <c r="C148" s="86" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D148" s="86" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="E148" s="86" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F148" s="86"/>
       <c r="G148" s="86" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="86" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="B149" s="86"/>
       <c r="C149" s="86" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D149" s="86" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="E149" s="86" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F149" s="86"/>
       <c r="G149" s="86" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="86" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="B150" s="86"/>
       <c r="C150" s="86" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D150" s="86" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="E150" s="86" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F150" s="86"/>
       <c r="G150" s="86" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="87" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="B151" s="87"/>
       <c r="C151" s="87" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D151" s="87" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="E151" s="87" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F151" s="87"/>
       <c r="G151" s="87" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="87" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="B152" s="87"/>
       <c r="C152" s="87" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D152" s="87" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="E152" s="87" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F152" s="87"/>
       <c r="G152" s="87" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="87" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="B153" s="87"/>
       <c r="C153" s="87" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D153" s="87" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="E153" s="87" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F153" s="87"/>
       <c r="G153" s="87" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="87" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="B154" s="87"/>
       <c r="C154" s="87" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D154" s="87" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="E154" s="87" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F154" s="87"/>
       <c r="G154" s="87" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="87" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="B155" s="87"/>
       <c r="C155" s="87" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D155" s="87" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="E155" s="87" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F155" s="87"/>
       <c r="G155" s="87" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="87" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="B156" s="87"/>
       <c r="C156" s="87" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D156" s="87" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="E156" s="87" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F156" s="87"/>
       <c r="G156" s="87" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="87" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="B157" s="87"/>
       <c r="C157" s="87" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D157" s="87" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="E157" s="87" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F157" s="87"/>
       <c r="G157" s="87" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="87" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="B158" s="87"/>
       <c r="C158" s="87" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D158" s="87" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="E158" s="87" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F158" s="87"/>
       <c r="G158" s="87" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="87" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="B159" s="87"/>
       <c r="C159" s="87" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D159" s="87" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="E159" s="87" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F159" s="87"/>
       <c r="G159" s="87" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="87" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="B160" s="87"/>
       <c r="C160" s="87" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D160" s="87" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="E160" s="87" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F160" s="87"/>
       <c r="G160" s="87" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="87" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="B161" s="87"/>
       <c r="C161" s="87" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D161" s="87" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="E161" s="87" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F161" s="87"/>
       <c r="G161" s="87" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="89" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="B162" s="89"/>
       <c r="C162" s="89" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D162" s="89"/>
       <c r="E162" s="89" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="F162" s="89" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="G162" s="89" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="91" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="B163" s="91"/>
       <c r="C163" s="91" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D163" s="91" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="E163" s="91" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F163" s="91"/>
       <c r="G163" s="91" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="94" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="B164" s="94"/>
       <c r="C164" s="94" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D164" s="94"/>
       <c r="E164" s="94" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="F164" s="94" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="G164" s="94" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="95" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="B165" s="95"/>
       <c r="C165" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D165" s="95" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="E165" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F165" s="95"/>
       <c r="G165" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="95" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="B166" s="95"/>
       <c r="C166" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D166" s="95" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="E166" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F166" s="95"/>
       <c r="G166" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="95" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="B167" s="95"/>
       <c r="C167" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D167" s="95" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="E167" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F167" s="95"/>
       <c r="G167" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="95" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="B168" s="95"/>
       <c r="C168" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D168" s="95" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="E168" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F168" s="95"/>
       <c r="G168" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="95" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="B169" s="95"/>
       <c r="C169" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D169" s="95" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="E169" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F169" s="95"/>
       <c r="G169" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="95" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="B170" s="95"/>
       <c r="C170" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D170" s="95" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="E170" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F170" s="95"/>
       <c r="G170" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="95" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="B171" s="95"/>
       <c r="C171" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D171" s="95" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="E171" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F171" s="95"/>
       <c r="G171" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="95" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="B172" s="95"/>
       <c r="C172" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D172" s="95" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="E172" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F172" s="95"/>
       <c r="G172" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="95" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="B173" s="95"/>
       <c r="C173" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D173" s="95" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="E173" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F173" s="95"/>
       <c r="G173" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="95" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="B174" s="95"/>
       <c r="C174" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D174" s="95" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="E174" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F174" s="95"/>
       <c r="G174" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="95" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="B175" s="95"/>
       <c r="C175" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D175" s="95" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="E175" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F175" s="95"/>
       <c r="G175" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="95" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="B176" s="95"/>
       <c r="C176" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D176" s="95" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="E176" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F176" s="95"/>
       <c r="G176" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="95" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="B177" s="95"/>
       <c r="C177" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D177" s="95" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="E177" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F177" s="95"/>
       <c r="G177" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="95" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="B178" s="95"/>
       <c r="C178" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D178" s="95" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="E178" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F178" s="95"/>
       <c r="G178" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="95" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="B179" s="95"/>
       <c r="C179" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D179" s="95" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="E179" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F179" s="95"/>
       <c r="G179" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="95" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="B180" s="95"/>
       <c r="C180" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D180" s="95" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="E180" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F180" s="95"/>
       <c r="G180" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="95" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="B181" s="95"/>
       <c r="C181" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D181" s="95" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="E181" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F181" s="95"/>
       <c r="G181" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="95" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="B182" s="95"/>
       <c r="C182" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D182" s="95" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="E182" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F182" s="95"/>
       <c r="G182" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="95" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="B183" s="95"/>
       <c r="C183" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D183" s="95" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="E183" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F183" s="95"/>
       <c r="G183" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="95" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="B184" s="95"/>
       <c r="C184" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D184" s="95" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="E184" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F184" s="95"/>
       <c r="G184" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="95" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="B185" s="95"/>
       <c r="C185" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D185" s="95" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="E185" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F185" s="95"/>
       <c r="G185" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="95" t="s">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="B186" s="95"/>
       <c r="C186" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D186" s="95" t="s">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="E186" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F186" s="95"/>
       <c r="G186" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="95" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B187" s="95"/>
       <c r="C187" s="95" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D187" s="95" t="s">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="E187" s="95" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F187" s="95"/>
       <c r="G187" s="95" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="96" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="B188" s="96"/>
       <c r="C188" s="96" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D188" s="96" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E188" s="96" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F188" s="96"/>
       <c r="G188" s="96" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="96" t="s">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="B189" s="96"/>
       <c r="C189" s="96" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D189" s="96" t="s">
-        <v>470</v>
+        <v>491</v>
       </c>
       <c r="E189" s="96" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F189" s="96"/>
       <c r="G189" s="96" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="96" t="s">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="B190" s="96"/>
       <c r="C190" s="96" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D190" s="96" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="E190" s="96" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F190" s="96"/>
       <c r="G190" s="96" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="96" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="B191" s="96"/>
       <c r="C191" s="96" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D191" s="96" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="E191" s="96" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F191" s="96"/>
       <c r="G191" s="96" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="97" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="B192" s="97"/>
       <c r="C192" s="97" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D192" s="97" t="s">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="E192" s="97" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F192" s="97"/>
       <c r="G192" s="97" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="97" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="B193" s="97"/>
       <c r="C193" s="97" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D193" s="97" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="E193" s="97" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F193" s="97"/>
       <c r="G193" s="97" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="98" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="B194" s="98"/>
       <c r="C194" s="98" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D194" s="98" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="E194" s="98" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F194" s="98"/>
       <c r="G194" s="98" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="99" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="B195" s="99"/>
       <c r="C195" s="99" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D195" s="99" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="E195" s="99" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F195" s="99"/>
       <c r="G195" s="99" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="100" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="B196" s="100"/>
       <c r="C196" s="100" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D196" s="100"/>
       <c r="E196" s="100" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="F196" s="100" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="G196" s="100" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="101" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="B197" s="101"/>
       <c r="C197" s="101" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D197" s="101"/>
       <c r="E197" s="101" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="F197" s="101" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="G197" s="101" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="102" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="B198" s="102"/>
       <c r="C198" s="102" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D198" s="102" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="E198" s="102" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F198" s="102"/>
       <c r="G198" s="102" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="102" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="B199" s="102"/>
       <c r="C199" s="102" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D199" s="102" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="E199" s="102" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F199" s="102"/>
       <c r="G199" s="102" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="102" t="s">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="B200" s="102"/>
       <c r="C200" s="102" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D200" s="102" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="E200" s="102" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F200" s="102"/>
       <c r="G200" s="102" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="102" t="s">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="B201" s="102"/>
       <c r="C201" s="102" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D201" s="102" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="E201" s="102" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F201" s="102"/>
       <c r="G201" s="102" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="102" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="B202" s="102"/>
       <c r="C202" s="102" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D202" s="102" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="E202" s="102" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F202" s="102"/>
       <c r="G202" s="102" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="102" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="B203" s="102"/>
       <c r="C203" s="102" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D203" s="102" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="E203" s="102" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F203" s="102"/>
       <c r="G203" s="102" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="102" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="B204" s="102"/>
       <c r="C204" s="102" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D204" s="102" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="E204" s="102" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F204" s="102"/>
       <c r="G204" s="102" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="102" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="B205" s="102"/>
       <c r="C205" s="102" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D205" s="102" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="E205" s="102" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F205" s="102"/>
       <c r="G205" s="102" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="102" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="B206" s="102"/>
       <c r="C206" s="102" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D206" s="102" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
       <c r="E206" s="102" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F206" s="102"/>
       <c r="G206" s="102" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="102" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="B207" s="102"/>
       <c r="C207" s="102" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D207" s="102" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="E207" s="102" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F207" s="102"/>
       <c r="G207" s="102" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="103" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="B208" s="103"/>
       <c r="C208" s="103" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D208" s="103" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="E208" s="103" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F208" s="103"/>
       <c r="G208" s="103" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="103" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="B209" s="103"/>
       <c r="C209" s="103" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D209" s="103" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="E209" s="103" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F209" s="103"/>
       <c r="G209" s="103" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="104" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="B210" s="104"/>
       <c r="C210" s="104" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D210" s="104" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="E210" s="104" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F210" s="104"/>
       <c r="G210" s="104" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="105" t="s">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="B211" s="105"/>
       <c r="C211" s="105" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D211" s="105" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="E211" s="105" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F211" s="105"/>
       <c r="G211" s="105" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="105" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="B212" s="105"/>
       <c r="C212" s="105" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D212" s="105" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="E212" s="105" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F212" s="105"/>
       <c r="G212" s="105" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="105" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="B213" s="105"/>
       <c r="C213" s="105" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D213" s="105" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="E213" s="105" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F213" s="105"/>
       <c r="G213" s="105" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="106" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="B214" s="106"/>
       <c r="C214" s="106" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D214" s="106" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="E214" s="106" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F214" s="106"/>
       <c r="G214" s="106" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="107" t="s">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="B215" s="107"/>
       <c r="C215" s="107" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D215" s="107" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="E215" s="107" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F215" s="107"/>
       <c r="G215" s="107" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="107" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="B216" s="107"/>
       <c r="C216" s="107" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D216" s="107" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="E216" s="107" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F216" s="107"/>
       <c r="G216" s="107" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="107" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="B217" s="107"/>
       <c r="C217" s="107" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D217" s="107" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="E217" s="107" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F217" s="107"/>
       <c r="G217" s="107" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="107" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="B218" s="107"/>
       <c r="C218" s="107" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D218" s="107" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="E218" s="107" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F218" s="107"/>
       <c r="G218" s="107" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="107" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="B219" s="107"/>
       <c r="C219" s="107" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D219" s="107" t="s">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="E219" s="107" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F219" s="107"/>
       <c r="G219" s="107" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="107" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="B220" s="107"/>
       <c r="C220" s="107" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D220" s="107" t="s">
-        <v>530</v>
+        <v>551</v>
       </c>
       <c r="E220" s="107" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F220" s="107"/>
       <c r="G220" s="107" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="107" t="s">
-        <v>531</v>
+        <v>552</v>
       </c>
       <c r="B221" s="107"/>
       <c r="C221" s="107" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D221" s="107" t="s">
-        <v>532</v>
+        <v>553</v>
       </c>
       <c r="E221" s="107" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F221" s="107"/>
       <c r="G221" s="107" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="107" t="s">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="B222" s="107"/>
       <c r="C222" s="107" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D222" s="107" t="s">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="E222" s="107" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F222" s="107"/>
       <c r="G222" s="107" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="107" t="s">
-        <v>535</v>
+        <v>556</v>
       </c>
       <c r="B223" s="107"/>
       <c r="C223" s="107" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D223" s="107" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="E223" s="107" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F223" s="107"/>
       <c r="G223" s="107" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="107" t="s">
-        <v>537</v>
+        <v>558</v>
       </c>
       <c r="B224" s="107"/>
       <c r="C224" s="107" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D224" s="107" t="s">
-        <v>538</v>
+        <v>559</v>
       </c>
       <c r="E224" s="107" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F224" s="107"/>
       <c r="G224" s="107" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="108" t="s">
-        <v>539</v>
+        <v>560</v>
       </c>
       <c r="B225" s="108"/>
       <c r="C225" s="108" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D225" s="108" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="E225" s="108" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F225" s="108"/>
       <c r="G225" s="108" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="109" t="s">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="B226" s="109"/>
       <c r="C226" s="109" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D226" s="109" t="s">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="E226" s="109" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F226" s="109"/>
       <c r="G226" s="109" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="109" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="B227" s="109"/>
       <c r="C227" s="109" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D227" s="109" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="E227" s="109" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F227" s="109"/>
       <c r="G227" s="109" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="109" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="B228" s="109"/>
       <c r="C228" s="109" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D228" s="109" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="E228" s="109" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F228" s="109"/>
       <c r="G228" s="109" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="109" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
       <c r="B229" s="109"/>
       <c r="C229" s="109" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D229" s="109" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="E229" s="109" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F229" s="109"/>
       <c r="G229" s="109" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="109" t="s">
-        <v>549</v>
+        <v>570</v>
       </c>
       <c r="B230" s="109"/>
       <c r="C230" s="109" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D230" s="109" t="s">
-        <v>550</v>
+        <v>571</v>
       </c>
       <c r="E230" s="109" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F230" s="109"/>
       <c r="G230" s="109" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="109" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
       <c r="B231" s="109"/>
       <c r="C231" s="109" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D231" s="109" t="s">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="E231" s="109" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F231" s="109"/>
       <c r="G231" s="109" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="110" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="B232" s="110"/>
       <c r="C232" s="110" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D232" s="110" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="E232" s="110" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F232" s="110"/>
       <c r="G232" s="110" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="110" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="B233" s="110"/>
       <c r="C233" s="110" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D233" s="110" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="E233" s="110" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F233" s="110"/>
       <c r="G233" s="110" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="111" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="B234" s="111"/>
       <c r="C234" s="111" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D234" s="111" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="E234" s="111" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F234" s="111"/>
       <c r="G234" s="111" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="111" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="B235" s="111"/>
       <c r="C235" s="111" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D235" s="111" t="s">
-        <v>560</v>
+        <v>581</v>
       </c>
       <c r="E235" s="111" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F235" s="111"/>
       <c r="G235" s="111" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="111" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="B236" s="111"/>
       <c r="C236" s="111" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D236" s="111" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="E236" s="111" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F236" s="111"/>
       <c r="G236" s="111" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="112" t="s">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="B237" s="112"/>
       <c r="C237" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D237" s="112" t="s">
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="E237" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F237" s="112"/>
       <c r="G237" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="112" t="s">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="B238" s="112"/>
       <c r="C238" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D238" s="112" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="E238" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F238" s="112"/>
       <c r="G238" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="112" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="B239" s="112"/>
       <c r="C239" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D239" s="112" t="s">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="E239" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F239" s="112"/>
       <c r="G239" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="112" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="B240" s="112"/>
       <c r="C240" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D240" s="112" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="E240" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F240" s="112"/>
       <c r="G240" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="112" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="B241" s="112"/>
       <c r="C241" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D241" s="112" t="s">
-        <v>572</v>
+        <v>593</v>
       </c>
       <c r="E241" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F241" s="112"/>
       <c r="G241" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="112" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="B242" s="112"/>
       <c r="C242" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D242" s="112" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="E242" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F242" s="112"/>
       <c r="G242" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="112" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="B243" s="112"/>
       <c r="C243" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D243" s="112" t="s">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="E243" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F243" s="112"/>
       <c r="G243" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="112" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="B244" s="112"/>
       <c r="C244" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D244" s="112" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="E244" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F244" s="112"/>
       <c r="G244" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="112" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="B245" s="112"/>
       <c r="C245" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D245" s="112" t="s">
-        <v>580</v>
+        <v>601</v>
       </c>
       <c r="E245" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F245" s="112"/>
       <c r="G245" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="112" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="B246" s="112"/>
       <c r="C246" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D246" s="112" t="s">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="E246" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F246" s="112"/>
       <c r="G246" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="112" t="s">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="B247" s="112"/>
       <c r="C247" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D247" s="112" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="E247" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F247" s="112"/>
       <c r="G247" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="112" t="s">
-        <v>585</v>
+        <v>606</v>
       </c>
       <c r="B248" s="112"/>
       <c r="C248" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D248" s="112" t="s">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="E248" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F248" s="112"/>
       <c r="G248" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="112" t="s">
-        <v>587</v>
+        <v>608</v>
       </c>
       <c r="B249" s="112"/>
       <c r="C249" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D249" s="112" t="s">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="E249" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F249" s="112"/>
       <c r="G249" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="112" t="s">
-        <v>589</v>
+        <v>610</v>
       </c>
       <c r="B250" s="112"/>
       <c r="C250" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D250" s="112" t="s">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="E250" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F250" s="112"/>
       <c r="G250" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="112" t="s">
-        <v>591</v>
+        <v>612</v>
       </c>
       <c r="B251" s="112"/>
       <c r="C251" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D251" s="112" t="s">
-        <v>592</v>
+        <v>613</v>
       </c>
       <c r="E251" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F251" s="112"/>
       <c r="G251" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="112" t="s">
-        <v>593</v>
+        <v>614</v>
       </c>
       <c r="B252" s="112"/>
       <c r="C252" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D252" s="112" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="E252" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F252" s="112"/>
       <c r="G252" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="112" t="s">
-        <v>595</v>
+        <v>616</v>
       </c>
       <c r="B253" s="112"/>
       <c r="C253" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D253" s="112" t="s">
-        <v>596</v>
+        <v>617</v>
       </c>
       <c r="E253" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F253" s="112"/>
       <c r="G253" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="112" t="s">
-        <v>597</v>
+        <v>618</v>
       </c>
       <c r="B254" s="112"/>
       <c r="C254" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D254" s="112" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="E254" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F254" s="112"/>
       <c r="G254" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="112" t="s">
-        <v>599</v>
+        <v>620</v>
       </c>
       <c r="B255" s="112"/>
       <c r="C255" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D255" s="112" t="s">
-        <v>600</v>
+        <v>621</v>
       </c>
       <c r="E255" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F255" s="112"/>
       <c r="G255" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="113" t="s">
-        <v>599</v>
+        <v>620</v>
       </c>
       <c r="B256" s="113"/>
       <c r="C256" s="113" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D256" s="113" t="s">
-        <v>600</v>
+        <v>621</v>
       </c>
       <c r="E256" s="113" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F256" s="113" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="G256" s="113" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="112" t="s">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="B257" s="112"/>
       <c r="C257" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D257" s="112" t="s">
-        <v>602</v>
+        <v>623</v>
       </c>
       <c r="E257" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F257" s="112"/>
       <c r="G257" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="112" t="s">
-        <v>603</v>
+        <v>624</v>
       </c>
       <c r="B258" s="112"/>
       <c r="C258" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D258" s="112" t="s">
-        <v>604</v>
+        <v>625</v>
       </c>
       <c r="E258" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F258" s="112"/>
       <c r="G258" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="112" t="s">
-        <v>605</v>
+        <v>626</v>
       </c>
       <c r="B259" s="112"/>
       <c r="C259" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D259" s="112" t="s">
-        <v>606</v>
+        <v>627</v>
       </c>
       <c r="E259" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F259" s="112"/>
       <c r="G259" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" s="112" t="s">
-        <v>607</v>
+        <v>628</v>
       </c>
       <c r="B260" s="112"/>
       <c r="C260" s="112" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D260" s="112" t="s">
-        <v>608</v>
+        <v>629</v>
       </c>
       <c r="E260" s="112" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F260" s="112"/>
       <c r="G260" s="112" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" s="114" t="s">
-        <v>609</v>
+        <v>630</v>
       </c>
       <c r="B261" s="114"/>
       <c r="C261" s="114" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D261" s="114" t="s">
-        <v>610</v>
+        <v>631</v>
       </c>
       <c r="E261" s="114" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F261" s="114"/>
       <c r="G261" s="114" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" s="114" t="s">
-        <v>611</v>
+        <v>632</v>
       </c>
       <c r="B262" s="114"/>
       <c r="C262" s="114" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D262" s="114" t="s">
-        <v>612</v>
+        <v>633</v>
       </c>
       <c r="E262" s="114" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F262" s="114"/>
       <c r="G262" s="114" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" s="115" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="B263" s="115"/>
       <c r="C263" s="115" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D263" s="115" t="s">
-        <v>614</v>
+        <v>635</v>
       </c>
       <c r="E263" s="115" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F263" s="115"/>
       <c r="G263" s="115" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" s="115" t="s">
-        <v>615</v>
+        <v>636</v>
       </c>
       <c r="B264" s="115"/>
       <c r="C264" s="115" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D264" s="115" t="s">
-        <v>616</v>
+        <v>637</v>
       </c>
       <c r="E264" s="115" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F264" s="115"/>
       <c r="G264" s="115" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="116" t="s">
-        <v>617</v>
+        <v>638</v>
       </c>
       <c r="B265" s="116"/>
       <c r="C265" s="116" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D265" s="116" t="s">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="E265" s="116" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F265" s="116"/>
       <c r="G265" s="116" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="117" t="s">
-        <v>619</v>
+        <v>640</v>
       </c>
       <c r="B266" s="117"/>
       <c r="C266" s="117" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D266" s="117" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="E266" s="117" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F266" s="117"/>
       <c r="G266" s="117" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" s="117" t="s">
-        <v>621</v>
+        <v>642</v>
       </c>
       <c r="B267" s="117"/>
       <c r="C267" s="117" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D267" s="117" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
       <c r="E267" s="117" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F267" s="117"/>
       <c r="G267" s="117" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" s="118" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
       <c r="B268" s="118"/>
       <c r="C268" s="118" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D268" s="118" t="s">
-        <v>624</v>
+        <v>645</v>
       </c>
       <c r="E268" s="118" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F268" s="118"/>
       <c r="G268" s="118" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="119" t="s">
-        <v>625</v>
+        <v>646</v>
       </c>
       <c r="B269" s="119"/>
       <c r="C269" s="119" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D269" s="119" t="s">
-        <v>626</v>
+        <v>647</v>
       </c>
       <c r="E269" s="119" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F269" s="119"/>
       <c r="G269" s="119" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" s="119" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="B270" s="119"/>
       <c r="C270" s="119" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D270" s="119" t="s">
-        <v>628</v>
+        <v>649</v>
       </c>
       <c r="E270" s="119" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F270" s="119"/>
       <c r="G270" s="119" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" s="119" t="s">
-        <v>629</v>
+        <v>650</v>
       </c>
       <c r="B271" s="119"/>
       <c r="C271" s="119" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D271" s="119" t="s">
-        <v>630</v>
+        <v>651</v>
       </c>
       <c r="E271" s="119" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F271" s="119"/>
       <c r="G271" s="119" t="s">
-        <v>106</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A272" s="134" t="s">
+        <v>652</v>
+      </c>
+      <c r="B272" s="134" t="s">
+        <v>44</v>
+      </c>
+      <c r="C272" s="134" t="s">
+        <v>115</v>
+      </c>
+      <c r="D272" s="134"/>
+      <c r="E272" s="134" t="s">
+        <v>653</v>
+      </c>
+      <c r="F272" s="134" t="s">
+        <v>289</v>
+      </c>
+      <c r="G272" s="134" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A273" s="134" t="s">
+        <v>654</v>
+      </c>
+      <c r="B273" s="134" t="s">
+        <v>44</v>
+      </c>
+      <c r="C273" s="134" t="s">
+        <v>115</v>
+      </c>
+      <c r="D273" s="134"/>
+      <c r="E273" s="134" t="s">
+        <v>653</v>
+      </c>
+      <c r="F273" s="134" t="s">
+        <v>655</v>
+      </c>
+      <c r="G273" s="134" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A274" s="134" t="s">
+        <v>656</v>
+      </c>
+      <c r="B274" s="134" t="s">
+        <v>44</v>
+      </c>
+      <c r="C274" s="134" t="s">
+        <v>115</v>
+      </c>
+      <c r="D274" s="134"/>
+      <c r="E274" s="134" t="s">
+        <v>653</v>
+      </c>
+      <c r="F274" s="134" t="s">
+        <v>655</v>
+      </c>
+      <c r="G274" s="134" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A275" s="134" t="s">
+        <v>657</v>
+      </c>
+      <c r="B275" s="134" t="s">
+        <v>44</v>
+      </c>
+      <c r="C275" s="134" t="s">
+        <v>115</v>
+      </c>
+      <c r="D275" s="134"/>
+      <c r="E275" s="134" t="s">
+        <v>653</v>
+      </c>
+      <c r="F275" s="134" t="s">
+        <v>289</v>
+      </c>
+      <c r="G275" s="134" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A276" s="135" t="s">
+        <v>658</v>
+      </c>
+      <c r="B276" s="135" t="s">
+        <v>44</v>
+      </c>
+      <c r="C276" s="135" t="s">
+        <v>115</v>
+      </c>
+      <c r="D276" s="135"/>
+      <c r="E276" s="135" t="s">
+        <v>116</v>
+      </c>
+      <c r="F276" s="135" t="s">
+        <v>659</v>
+      </c>
+      <c r="G276" s="135" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A277" s="135" t="s">
+        <v>660</v>
+      </c>
+      <c r="B277" s="135" t="s">
+        <v>44</v>
+      </c>
+      <c r="C277" s="135" t="s">
+        <v>115</v>
+      </c>
+      <c r="D277" s="135"/>
+      <c r="E277" s="135" t="s">
+        <v>116</v>
+      </c>
+      <c r="F277" s="135" t="s">
+        <v>659</v>
+      </c>
+      <c r="G277" s="135" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A278" s="135" t="s">
+        <v>661</v>
+      </c>
+      <c r="B278" s="135" t="s">
+        <v>44</v>
+      </c>
+      <c r="C278" s="135" t="s">
+        <v>115</v>
+      </c>
+      <c r="D278" s="135"/>
+      <c r="E278" s="135" t="s">
+        <v>116</v>
+      </c>
+      <c r="F278" s="135" t="s">
+        <v>662</v>
+      </c>
+      <c r="G278" s="135" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A279" s="136" t="s">
+        <v>663</v>
+      </c>
+      <c r="B279" s="136" t="s">
+        <v>44</v>
+      </c>
+      <c r="C279" s="136" t="s">
+        <v>115</v>
+      </c>
+      <c r="D279" s="136"/>
+      <c r="E279" s="136" t="s">
+        <v>664</v>
+      </c>
+      <c r="F279" s="136" t="s">
+        <v>121</v>
+      </c>
+      <c r="G279" s="136" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
